--- a/XlsxSharp.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -36,7 +36,7 @@
     <x:t>GetFormattedString()</x:t>
   </x:si>
   <x:si>
-    <x:t>9/2/2010 12:00:00 AM</x:t>
+    <x:t>9/2/2010 12:00:00 AM</x:t>
   </x:si>
   <x:si>
     <x:t>2010-Sep-02</x:t>

--- a/XlsxSharp.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -36,7 +36,7 @@
     <x:t>GetFormattedString()</x:t>
   </x:si>
   <x:si>
-    <x:t>9/2/2010 12:00:00 AM</x:t>
+    <x:t>9/2/2010 12:00:00 AM</x:t>
   </x:si>
   <x:si>
     <x:t>2010-Sep-02</x:t>
